--- a/GUA/IPPU/A1_Outputs/A-O_Demand.xlsx
+++ b/GUA/IPPU/A1_Outputs/A-O_Demand.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\M0_IPPU\A1_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IgnacioAlfaroCorrale\Desktop\Models_running\0_guatemala_2025\IPPU_GUA_v1_2025\A1_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8500EF4-6264-4E7A-9F47-846768C24ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF095414-F15A-45D3-9D12-58F9A50D8263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand_Projection" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Demand_Projection!$A$1:$AO$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="39">
   <si>
     <t>Demand/Share</t>
   </si>
@@ -62,28 +65,104 @@
     <t>Demand</t>
   </si>
   <si>
+    <t>E5INDCEM_PROD</t>
+  </si>
+  <si>
+    <t>E5IPPUPARAFFIN</t>
+  </si>
+  <si>
+    <t>Demand Industrial Cement production</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Paraffin Wax</t>
+  </si>
+  <si>
     <t>not needed</t>
   </si>
   <si>
-    <t>Otro</t>
-  </si>
-  <si>
-    <t>E5_CEM_PRODCEM_PROD</t>
-  </si>
-  <si>
-    <t>Demand Cement production Cement production</t>
+    <t>User defined</t>
+  </si>
+  <si>
+    <t>E5IPPULUBRI_OILS</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Use of Lubricants Oils</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC32</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC32</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC125</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC125</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC134a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC134a</t>
+  </si>
+  <si>
+    <t>E5IPPUREFR_AC_HFC143a</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Refrigeration and air conditioning HFC143a</t>
+  </si>
+  <si>
+    <t>E5IPPUPROD_FERRO</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Ferroalloy production</t>
+  </si>
+  <si>
+    <t>E5IPPUGLASS_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Glass production</t>
+  </si>
+  <si>
+    <t>E5IPPUIRON_STEEL</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Iron and Steel production</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_CAL_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production calcitic</t>
+  </si>
+  <si>
+    <t>E5IPPULIME_DOL_PROD</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Lime production dolomitic</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_CERAMICS</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate ceramics</t>
+  </si>
+  <si>
+    <t>E5IPPUCARBONATE_ASH</t>
+  </si>
+  <si>
+    <t>Demand Industrial Processes Carbonate soda ash</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +172,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -116,7 +188,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -145,21 +217,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Millares [0] 2" xfId="1" xr:uid="{56BAFE40-C50B-48FF-A151-AC7134CA97EC}"/>
-    <cellStyle name="Millares 2" xfId="2" xr:uid="{EA5F18AE-7BEB-4BB4-9C70-1A8440431B88}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,17 +531,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO2"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AO15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="12" max="41" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="23" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="41" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.3">
@@ -601,142 +672,1769 @@
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>2.7545999999999999</v>
+      </c>
+      <c r="J2" s="3">
+        <v>3.0038999999999998</v>
+      </c>
+      <c r="K2" s="3">
+        <v>3.5249999999999999</v>
+      </c>
+      <c r="L2" s="3">
+        <v>4.2774999999999999</v>
+      </c>
+      <c r="M2" s="3">
+        <v>4.6204000000000001</v>
+      </c>
+      <c r="N2" s="3">
+        <v>5.7080000000000002</v>
+      </c>
+      <c r="O2" s="3">
+        <v>6.0960999999999999</v>
+      </c>
+      <c r="P2" s="3">
+        <v>6.5106999999999999</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>6.9534000000000002</v>
+      </c>
+      <c r="R2" s="3">
+        <v>7.4261999999999997</v>
+      </c>
+      <c r="S2" s="3">
+        <v>7.9311999999999996</v>
+      </c>
+      <c r="T2" s="3">
+        <v>8.4704999999999995</v>
+      </c>
+      <c r="U2" s="3">
+        <v>9.0465</v>
+      </c>
+      <c r="V2" s="3">
+        <v>9.6616999999999997</v>
+      </c>
+      <c r="W2" s="3">
+        <v>10.3187</v>
+      </c>
+      <c r="X2" s="3">
+        <v>11.0204</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>11.7698</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>12.5701</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>13.424899999999999</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>14.3378</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>15.3127</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>16.353999999999999</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>17.466100000000001</v>
+      </c>
+      <c r="AF2" s="3">
+        <v>18.6538</v>
+      </c>
+      <c r="AG2" s="3">
+        <v>19.9222</v>
+      </c>
+      <c r="AH2" s="3">
+        <v>21.276900000000001</v>
+      </c>
+      <c r="AI2" s="3">
+        <v>22.723800000000001</v>
+      </c>
+      <c r="AJ2" s="3">
+        <v>24.268999999999998</v>
+      </c>
+      <c r="AK2" s="3">
+        <v>25.9193</v>
+      </c>
+      <c r="AL2" s="3">
+        <v>27.681799999999999</v>
+      </c>
+      <c r="AM2" s="3">
+        <v>29.5641</v>
+      </c>
+      <c r="AN2" s="3">
+        <v>31.5745</v>
+      </c>
+      <c r="AO2" s="3">
+        <v>33.721600000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.24360000000000001</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.32390000000000002</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.42349999999999999</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.40079999999999999</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.4703</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.48820000000000002</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0.50680000000000003</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0.56669999999999998</v>
+      </c>
+      <c r="S3" s="3">
+        <v>0.58830000000000005</v>
+      </c>
+      <c r="T3" s="3">
+        <v>0.61060000000000003</v>
+      </c>
+      <c r="U3" s="3">
+        <v>0.63380000000000003</v>
+      </c>
+      <c r="V3" s="3">
+        <v>0.65790000000000004</v>
+      </c>
+      <c r="W3" s="3">
+        <v>0.68289999999999995</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.70889999999999997</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>0.73580000000000001</v>
+      </c>
+      <c r="Z3" s="3">
+        <v>0.76380000000000003</v>
+      </c>
+      <c r="AA3" s="3">
+        <v>0.79279999999999995</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0.82289999999999996</v>
+      </c>
+      <c r="AC3" s="3">
+        <v>0.85419999999999996</v>
+      </c>
+      <c r="AD3" s="3">
+        <v>0.88670000000000004</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>0.9204</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0.95530000000000004</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.99160000000000004</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>1.0293000000000001</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>1.0684</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>1.109</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>1.1512</v>
+      </c>
+      <c r="AL3" s="3">
+        <v>1.1949000000000001</v>
+      </c>
+      <c r="AM3" s="3">
+        <v>1.2403</v>
+      </c>
+      <c r="AN3" s="3">
+        <v>1.2875000000000001</v>
+      </c>
+      <c r="AO3" s="3">
+        <v>1.3364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1.8800000000000001E-2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0.1081</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0.1169</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.12130000000000001</v>
+      </c>
+      <c r="O4" s="3">
+        <v>0.12590000000000001</v>
+      </c>
+      <c r="P4" s="3">
+        <v>0.13070000000000001</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>0.1356</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0.14080000000000001</v>
+      </c>
+      <c r="S4" s="3">
+        <v>0.1462</v>
+      </c>
+      <c r="T4" s="3">
+        <v>0.1517</v>
+      </c>
+      <c r="U4" s="3">
+        <v>0.1575</v>
+      </c>
+      <c r="V4" s="3">
+        <v>0.16350000000000001</v>
+      </c>
+      <c r="W4" s="3">
+        <v>0.16969999999999999</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.17610000000000001</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0.18279999999999999</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>0.1898</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0.20449999999999999</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0.2122</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0.2203</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>0.22869999999999999</v>
+      </c>
+      <c r="AF4" s="3">
+        <v>0.23730000000000001</v>
+      </c>
+      <c r="AG4" s="3">
+        <v>0.24640000000000001</v>
+      </c>
+      <c r="AH4" s="3">
+        <v>0.25569999999999998</v>
+      </c>
+      <c r="AI4" s="3">
+        <v>0.26540000000000002</v>
+      </c>
+      <c r="AJ4" s="3">
+        <v>0.27550000000000002</v>
+      </c>
+      <c r="AK4" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="AL4" s="3">
+        <v>0.2969</v>
+      </c>
+      <c r="AM4" s="3">
+        <v>0.30809999999999998</v>
+      </c>
+      <c r="AN4" s="3">
+        <v>0.31990000000000002</v>
+      </c>
+      <c r="AO4" s="3">
+        <v>0.33200000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.11459999999999999</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.13750000000000001</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0.17960000000000001</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0.19789999999999999</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0.1714</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.1779</v>
+      </c>
+      <c r="O5" s="3">
+        <v>0.18459999999999999</v>
+      </c>
+      <c r="P5" s="3">
+        <v>0.19170000000000001</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>0.19889999999999999</v>
+      </c>
+      <c r="R5" s="3">
+        <v>0.20649999999999999</v>
+      </c>
+      <c r="S5" s="3">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="T5" s="3">
+        <v>0.2225</v>
+      </c>
+      <c r="U5" s="3">
+        <v>0.23089999999999999</v>
+      </c>
+      <c r="V5" s="3">
+        <v>0.2397</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0.24879999999999999</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0.25829999999999997</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0.2681</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>0.27829999999999999</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>0.28889999999999999</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>0.29980000000000001</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="AD5" s="3">
+        <v>0.3231</v>
+      </c>
+      <c r="AE5" s="3">
+        <v>0.33529999999999999</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>0.34810000000000002</v>
+      </c>
+      <c r="AG5" s="3">
+        <v>0.36130000000000001</v>
+      </c>
+      <c r="AH5" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="AI5" s="3">
+        <v>0.38929999999999998</v>
+      </c>
+      <c r="AJ5" s="3">
+        <v>0.40410000000000001</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>0.4194</v>
+      </c>
+      <c r="AL5" s="3">
+        <v>0.43540000000000001</v>
+      </c>
+      <c r="AM5" s="3">
+        <v>0.45190000000000002</v>
+      </c>
+      <c r="AN5" s="3">
+        <v>0.46910000000000002</v>
+      </c>
+      <c r="AO5" s="3">
+        <v>0.4869</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5.9299999999999999E-2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K6" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="L6" s="3">
+        <v>2.4799999999999999E-2</v>
+      </c>
+      <c r="M6" s="3">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="N6" s="3">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="O6" s="3">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="P6" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="R6" s="3">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="S6" s="3">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="T6" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="U6" s="3">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="V6" s="3">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="W6" s="3">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="X6" s="3">
+        <v>4.53E-2</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>4.7E-2</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>4.8800000000000003E-2</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>5.4600000000000003E-2</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>5.67E-2</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="AF6" s="3">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="AG6" s="3">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="AH6" s="3">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="AI6" s="3">
+        <v>6.83E-2</v>
+      </c>
+      <c r="AJ6" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>7.6399999999999996E-2</v>
+      </c>
+      <c r="AM6" s="3">
+        <v>7.9299999999999995E-2</v>
+      </c>
+      <c r="AN6" s="3">
+        <v>8.2299999999999998E-2</v>
+      </c>
+      <c r="AO6" s="3">
+        <v>8.5400000000000004E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="J7" s="3">
+        <v>3.0800000000000001E-2</v>
+      </c>
+      <c r="K7" s="3">
+        <v>2.8799999999999999E-2</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3.56E-2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>3.8100000000000002E-2</v>
+      </c>
+      <c r="O7" s="3">
+        <v>3.9600000000000003E-2</v>
+      </c>
+      <c r="P7" s="3">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="R7" s="3">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="S7" s="3">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="T7" s="3">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="U7" s="3">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="V7" s="3">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="W7" s="3">
+        <v>5.33E-2</v>
+      </c>
+      <c r="X7" s="3">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="Z7" s="3">
+        <v>5.96E-2</v>
+      </c>
+      <c r="AA7" s="3">
+        <v>6.1899999999999997E-2</v>
+      </c>
+      <c r="AB7" s="3">
+        <v>6.4299999999999996E-2</v>
+      </c>
+      <c r="AC7" s="3">
+        <v>6.6699999999999995E-2</v>
+      </c>
+      <c r="AD7" s="3">
+        <v>6.9199999999999998E-2</v>
+      </c>
+      <c r="AE7" s="3">
+        <v>7.1900000000000006E-2</v>
+      </c>
+      <c r="AF7" s="3">
+        <v>7.46E-2</v>
+      </c>
+      <c r="AG7" s="3">
+        <v>7.7399999999999997E-2</v>
+      </c>
+      <c r="AH7" s="3">
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="AI7" s="3">
+        <v>8.3400000000000002E-2</v>
+      </c>
+      <c r="AJ7" s="3">
+        <v>8.6599999999999996E-2</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>8.9899999999999994E-2</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>9.3299999999999994E-2</v>
+      </c>
+      <c r="AM7" s="3">
+        <v>9.6799999999999997E-2</v>
+      </c>
+      <c r="AN7" s="3">
+        <v>0.10050000000000001</v>
+      </c>
+      <c r="AO7" s="3">
+        <v>0.1043</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.29399999999999998</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0.30690000000000001</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0.27110000000000001</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0.13350000000000001</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.1386</v>
+      </c>
+      <c r="O8" s="3">
+        <v>0.14380000000000001</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.14929999999999999</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.155</v>
+      </c>
+      <c r="R8" s="3">
+        <v>0.16089999999999999</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.17330000000000001</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0.1799</v>
+      </c>
+      <c r="V8" s="3">
+        <v>0.1867</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0.1938</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.20119999999999999</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0.2089</v>
+      </c>
+      <c r="Z8" s="3">
+        <v>0.21679999999999999</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0.2336</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0.24249999999999999</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0.25169999999999998</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0.26119999999999999</v>
+      </c>
+      <c r="AF8" s="3">
+        <v>0.2712</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0.28149999999999997</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0.29220000000000002</v>
+      </c>
+      <c r="AI8" s="3">
+        <v>0.30330000000000001</v>
+      </c>
+      <c r="AJ8" s="3">
+        <v>0.31480000000000002</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0.32679999999999998</v>
+      </c>
+      <c r="AL8" s="3">
+        <v>0.3392</v>
+      </c>
+      <c r="AM8" s="3">
+        <v>0.35210000000000002</v>
+      </c>
+      <c r="AN8" s="3">
+        <v>0.3654</v>
+      </c>
+      <c r="AO8" s="3">
+        <v>0.37930000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0.3735</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.47289999999999999</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0.57240000000000002</v>
+      </c>
+      <c r="L9" s="3">
+        <v>6.0499999999999998E-2</v>
+      </c>
+      <c r="M9" s="3">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="N9" s="3">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O9" s="3">
+        <v>3.0099999999999998E-2</v>
+      </c>
+      <c r="P9" s="3">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>3.2399999999999998E-2</v>
+      </c>
+      <c r="R9" s="3">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="S9" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="T9" s="3">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="U9" s="3">
+        <v>3.7600000000000001E-2</v>
+      </c>
+      <c r="V9" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="W9" s="3">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="X9" s="3">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>4.53E-2</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>4.7100000000000003E-2</v>
+      </c>
+      <c r="AB9" s="3">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="AC9" s="3">
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>5.4600000000000003E-2</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>5.67E-2</v>
+      </c>
+      <c r="AG9" s="3">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>6.1100000000000002E-2</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>6.5799999999999997E-2</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>6.83E-2</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="AM9" s="3">
+        <v>7.3599999999999999E-2</v>
+      </c>
+      <c r="AN9" s="3">
+        <v>7.6399999999999996E-2</v>
+      </c>
+      <c r="AO9" s="3">
+        <v>7.9299999999999995E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="J10" s="3">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="K10" s="3">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="L10" s="3">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="M10" s="3">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="N10" s="3">
+        <v>6.2E-2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>6.4399999999999999E-2</v>
+      </c>
+      <c r="P10" s="3">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="R10" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="S10" s="3">
+        <v>7.4700000000000003E-2</v>
+      </c>
+      <c r="T10" s="3">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="U10" s="3">
+        <v>8.0500000000000002E-2</v>
+      </c>
+      <c r="V10" s="3">
+        <v>8.3599999999999994E-2</v>
+      </c>
+      <c r="W10" s="3">
+        <v>8.6800000000000002E-2</v>
+      </c>
+      <c r="X10" s="3">
+        <v>9.01E-2</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>9.35E-2</v>
+      </c>
+      <c r="Z10" s="3">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0.1007</v>
+      </c>
+      <c r="AB10" s="3">
+        <v>0.1045</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>0.1085</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>0.11260000000000001</v>
+      </c>
+      <c r="AE10" s="3">
+        <v>0.1169</v>
+      </c>
+      <c r="AF10" s="3">
+        <v>0.12139999999999999</v>
+      </c>
+      <c r="AG10" s="3">
+        <v>0.126</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0.1308</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0.13569999999999999</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>0.1409</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0.1462</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0.15179999999999999</v>
+      </c>
+      <c r="AM10" s="3">
+        <v>0.15759999999999999</v>
+      </c>
+      <c r="AN10" s="3">
+        <v>0.1636</v>
+      </c>
+      <c r="AO10" s="3">
+        <v>0.16980000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2">
+      <c r="D11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="2">
         <v>0</v>
       </c>
-      <c r="I2" s="2">
-        <v>2.7540480030306465</v>
-      </c>
-      <c r="J2" s="2">
-        <v>2.8670200000000001</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2.92</v>
-      </c>
-      <c r="L2" s="2">
-        <v>3.6211199999999995</v>
-      </c>
-      <c r="M2" s="2">
-        <v>3.8986000000000001</v>
-      </c>
-      <c r="N2" s="2">
-        <v>5.7080000000000002</v>
-      </c>
-      <c r="O2" s="2">
-        <v>6.0961440000000007</v>
-      </c>
-      <c r="P2" s="2">
-        <v>6.5106817920000006</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>6.9534081538560004</v>
-      </c>
-      <c r="R2" s="2">
-        <v>7.4262399083182098</v>
-      </c>
-      <c r="S2" s="2">
-        <v>7.9312242220838396</v>
-      </c>
-      <c r="T2" s="2">
-        <v>8.4705474691855507</v>
-      </c>
-      <c r="U2" s="2">
-        <v>9.0465446970901588</v>
-      </c>
-      <c r="V2" s="2">
-        <v>9.6617097364923001</v>
-      </c>
-      <c r="W2" s="2">
-        <v>10.3187059985737</v>
-      </c>
-      <c r="X2" s="2">
-        <v>11.020378006476699</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>11.7697637109172</v>
-      </c>
-      <c r="Z2" s="2">
-        <v>12.570107643259501</v>
-      </c>
-      <c r="AA2" s="2">
-        <v>13.424874963001201</v>
-      </c>
-      <c r="AB2" s="2">
-        <v>14.3377664604853</v>
-      </c>
-      <c r="AC2" s="2">
-        <v>15.312734579798299</v>
-      </c>
-      <c r="AD2" s="2">
-        <v>16.3540005312246</v>
-      </c>
-      <c r="AE2" s="2">
-        <v>17.466072567347801</v>
-      </c>
-      <c r="AF2" s="2">
-        <v>18.653765501927502</v>
-      </c>
-      <c r="AG2" s="2">
-        <v>19.922221556058602</v>
-      </c>
-      <c r="AH2" s="2">
-        <v>21.2769326218706</v>
-      </c>
-      <c r="AI2" s="2">
-        <v>22.7237640401578</v>
-      </c>
-      <c r="AJ2" s="2">
-        <v>24.2689799948885</v>
-      </c>
-      <c r="AK2" s="2">
-        <v>25.919270634540897</v>
-      </c>
-      <c r="AL2" s="2">
-        <v>27.681781037689699</v>
-      </c>
-      <c r="AM2" s="2">
-        <v>29.5641421482526</v>
-      </c>
-      <c r="AN2" s="2">
-        <v>31.574503814333799</v>
-      </c>
-      <c r="AO2" s="2">
-        <v>33.721570073708499</v>
+      <c r="I11" s="3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="J11" s="3">
+        <v>1.9E-3</v>
+      </c>
+      <c r="K11" s="3">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1.67E-2</v>
+      </c>
+      <c r="N11" s="3">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="O11" s="3">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1.8599999999999998E-2</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="R11" s="3">
+        <v>2.01E-2</v>
+      </c>
+      <c r="S11" s="3">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="T11" s="3">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="U11" s="3">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="V11" s="3">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="W11" s="3">
+        <v>2.4199999999999999E-2</v>
+      </c>
+      <c r="X11" s="3">
+        <v>2.5100000000000001E-2</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="Z11" s="3">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="AA11" s="3">
+        <v>2.81E-2</v>
+      </c>
+      <c r="AB11" s="3">
+        <v>2.92E-2</v>
+      </c>
+      <c r="AC11" s="3">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="AD11" s="3">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="AE11" s="3">
+        <v>3.2599999999999997E-2</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>3.39E-2</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="AI11" s="3">
+        <v>3.7900000000000003E-2</v>
+      </c>
+      <c r="AJ11" s="3">
+        <v>3.9300000000000002E-2</v>
+      </c>
+      <c r="AK11" s="3">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="AL11" s="3">
+        <v>4.24E-2</v>
+      </c>
+      <c r="AM11" s="3">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AN11" s="3">
+        <v>4.5600000000000002E-2</v>
+      </c>
+      <c r="AO11" s="3">
+        <v>4.7399999999999998E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1.6500000000000001E-2</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="M12" s="3">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="N12" s="3">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>5.45E-2</v>
+      </c>
+      <c r="P12" s="3">
+        <v>5.5899999999999998E-2</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>5.7299999999999997E-2</v>
+      </c>
+      <c r="R12" s="3">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="S12" s="3">
+        <v>6.0199999999999997E-2</v>
+      </c>
+      <c r="T12" s="3">
+        <v>6.1699999999999998E-2</v>
+      </c>
+      <c r="U12" s="3">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="V12" s="3">
+        <v>6.4799999999999996E-2</v>
+      </c>
+      <c r="W12" s="3">
+        <v>6.6500000000000004E-2</v>
+      </c>
+      <c r="X12" s="3">
+        <v>6.8099999999999994E-2</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>6.9800000000000001E-2</v>
+      </c>
+      <c r="Z12" s="3">
+        <v>7.1599999999999997E-2</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>7.3400000000000007E-2</v>
+      </c>
+      <c r="AB12" s="3">
+        <v>7.5200000000000003E-2</v>
+      </c>
+      <c r="AC12" s="3">
+        <v>7.7100000000000002E-2</v>
+      </c>
+      <c r="AD12" s="3">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AE12" s="3">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>8.5099999999999995E-2</v>
+      </c>
+      <c r="AH12" s="3">
+        <v>8.72E-2</v>
+      </c>
+      <c r="AI12" s="3">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="AK12" s="3">
+        <v>9.3899999999999997E-2</v>
+      </c>
+      <c r="AL12" s="3">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="AM12" s="3">
+        <v>9.8699999999999996E-2</v>
+      </c>
+      <c r="AN12" s="3">
+        <v>0.1011</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0.1037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>2.9100000000000001E-2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="M13" s="3">
+        <v>4.2900000000000001E-2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="O13" s="3">
+        <v>4.5100000000000001E-2</v>
+      </c>
+      <c r="P13" s="3">
+        <v>4.6199999999999998E-2</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>4.7399999999999998E-2</v>
+      </c>
+      <c r="R13" s="3">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="S13" s="3">
+        <v>4.9799999999999997E-2</v>
+      </c>
+      <c r="T13" s="3">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="U13" s="3">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="V13" s="3">
+        <v>5.3600000000000002E-2</v>
+      </c>
+      <c r="W13" s="3">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="X13" s="3">
+        <v>5.6300000000000003E-2</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>5.9200000000000003E-2</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>6.0600000000000001E-2</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>6.2199999999999998E-2</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>6.5299999999999997E-2</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>6.6900000000000001E-2</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>6.8599999999999994E-2</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>7.3899999999999993E-2</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>7.5700000000000003E-2</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>7.7600000000000002E-2</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>7.9600000000000004E-2</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>8.1600000000000006E-2</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>8.3599999999999994E-2</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>8.5699999999999998E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>6.4899999999999999E-2</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.1002</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.13969999999999999</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0.14319999999999999</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0.15049999999999999</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0.1542</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0.15809999999999999</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0.1661</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0.17019999999999999</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0.17449999999999999</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0.1789</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0.18329999999999999</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0.18790000000000001</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0.19259999999999999</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0.19739999999999999</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0.2024</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0.2074</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0.21260000000000001</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0.21790000000000001</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0.22339999999999999</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0.22889999999999999</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0.23469999999999999</v>
+      </c>
+      <c r="AI14" s="3">
+        <v>0.24049999999999999</v>
+      </c>
+      <c r="AJ14" s="3">
+        <v>0.2465</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0.25269999999999998</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="AM14" s="3">
+        <v>0.26550000000000001</v>
+      </c>
+      <c r="AN14" s="3">
+        <v>0.27210000000000001</v>
+      </c>
+      <c r="AO14" s="3">
+        <v>0.27889999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2.35E-2</v>
+      </c>
+      <c r="K15" s="3">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="L15" s="3">
+        <v>3.09E-2</v>
+      </c>
+      <c r="M15" s="3">
+        <v>3.6299999999999999E-2</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="O15" s="3">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="P15" s="3">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="R15" s="3">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="S15" s="3">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="T15" s="3">
+        <v>4.3200000000000002E-2</v>
+      </c>
+      <c r="U15" s="3">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="V15" s="3">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="W15" s="3">
+        <v>4.65E-2</v>
+      </c>
+      <c r="X15" s="3">
+        <v>4.7699999999999999E-2</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>5.0099999999999999E-2</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="AC15" s="3">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>5.5300000000000002E-2</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>5.67E-2</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>5.8099999999999999E-2</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>5.9499999999999997E-2</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>6.25E-2</v>
+      </c>
+      <c r="AJ15" s="3">
+        <v>6.4100000000000004E-2</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>6.5699999999999995E-2</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>6.7299999999999999E-2</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="AN15" s="3">
+        <v>7.0800000000000002E-2</v>
+      </c>
+      <c r="AO15" s="3">
+        <v>7.2499999999999995E-2</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -963,27 +2661,49 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA2CB30-993F-4911-B443-10FFE1831DEE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C756FE05-CBF4-44B6-8340-45CDBB159352}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="48eed89a-7418-4977-ae3a-838f0fac8ec5"/>
+    <ds:schemaRef ds:uri="416d42ac-85ec-40c4-8054-6c816fd4b6a7"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671DC943-CF13-4323-99FF-C6ED9E11551A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E7DDA92-5807-4D4E-BF7E-004F548F55E0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
+    <ds:schemaRef ds:uri="081a93ea-d517-42a5-a2b7-457060aa7471"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BFF214D-7EE4-4F67-B4E8-96A27647379E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48A91C3-5182-424C-ABB6-C45673A36CDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>